--- a/Broker_Analysis.xlsx
+++ b/Broker_Analysis.xlsx
@@ -435,10 +435,1871 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:F93"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Net Holding Brokers (1 M)</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Top 1</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Top 2</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Top 3</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Top 4</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Top 5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>B1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>SHPC/46511/614.32</v>
+      </c>
+      <c r="C2" t="str">
+        <v>CHDC/10685/2,684.69</v>
+      </c>
+      <c r="D2" t="str">
+        <v>SLBBL/27006/999.21</v>
+      </c>
+      <c r="E2" t="str">
+        <v>RADHI/30183/801.82</v>
+      </c>
+      <c r="F2" t="str">
+        <v>SAPDBL/15027/1,057.64</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>B3</v>
+      </c>
+      <c r="B3" t="str">
+        <v>NBL/31596/257.69</v>
+      </c>
+      <c r="C3" t="str">
+        <v>KKHC/17810/357.24</v>
+      </c>
+      <c r="D3" t="str">
+        <v>KSBBL/11012/520.52</v>
+      </c>
+      <c r="E3" t="str">
+        <v>HRL/4787/960.83</v>
+      </c>
+      <c r="F3" t="str">
+        <v>SHPC/8148/603.38</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>B4</v>
+      </c>
+      <c r="B4" t="str">
+        <v>SBL/261082/347.07</v>
+      </c>
+      <c r="C4" t="str">
+        <v>SHL/130761/570.64</v>
+      </c>
+      <c r="D4" t="str">
+        <v>SPDL/64631/423.90</v>
+      </c>
+      <c r="E4" t="str">
+        <v>CHDC/8648/2,628.31</v>
+      </c>
+      <c r="F4" t="str">
+        <v>SCB/27161/645.69</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>B5</v>
+      </c>
+      <c r="B5" t="str">
+        <v>GFCL/22450/709.38</v>
+      </c>
+      <c r="C5" t="str">
+        <v>SHPC/26774/604.44</v>
+      </c>
+      <c r="D5" t="str">
+        <v>UPCL/35123/411.92</v>
+      </c>
+      <c r="E5" t="str">
+        <v>CHDC/4695/2,654.22</v>
+      </c>
+      <c r="F5" t="str">
+        <v>MLBBL/5421/1,594.21</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>B6</v>
+      </c>
+      <c r="B6" t="str">
+        <v>BPCL/45053/869.95</v>
+      </c>
+      <c r="C6" t="str">
+        <v>UPCL/100244/409.04</v>
+      </c>
+      <c r="D6" t="str">
+        <v>NGPL/83797/395.38</v>
+      </c>
+      <c r="E6" t="str">
+        <v>SPIL/39267/804.60</v>
+      </c>
+      <c r="F6" t="str">
+        <v>NICA/72679/397.72</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>B7</v>
+      </c>
+      <c r="B7" t="str">
+        <v>HIDCLP/184078/208.29</v>
+      </c>
+      <c r="C7" t="str">
+        <v>HRL/18041/993.73</v>
+      </c>
+      <c r="D7" t="str">
+        <v>SAPDBL/15024/1,058.92</v>
+      </c>
+      <c r="E7" t="str">
+        <v>HDL/11225/1,236.58</v>
+      </c>
+      <c r="F7" t="str">
+        <v>NLIC/15322/802.42</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>B8</v>
+      </c>
+      <c r="B8" t="str">
+        <v>RADHI/60501/801.28</v>
+      </c>
+      <c r="C8" t="str">
+        <v>NGPL/96907/400.61</v>
+      </c>
+      <c r="D8" t="str">
+        <v>BARUN/41941/423.67</v>
+      </c>
+      <c r="E8" t="str">
+        <v>NABBC/10388/1,609.20</v>
+      </c>
+      <c r="F8" t="str">
+        <v>SHEL/40286/298.05</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>B10</v>
+      </c>
+      <c r="B9" t="str">
+        <v>RFPL/91580/610.95</v>
+      </c>
+      <c r="C9" t="str">
+        <v>HDL/17321/1,204.43</v>
+      </c>
+      <c r="D9" t="str">
+        <v>HRL/17205/927.60</v>
+      </c>
+      <c r="E9" t="str">
+        <v>SAHAS/18560/601.06</v>
+      </c>
+      <c r="F9" t="str">
+        <v>LEC/46229/213.98</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>B11</v>
+      </c>
+      <c r="B10" t="str">
+        <v>EBL/105823/700.87</v>
+      </c>
+      <c r="C10" t="str">
+        <v>NMB/71925/263.76</v>
+      </c>
+      <c r="D10" t="str">
+        <v>SAPDBL/11939/1,062.07</v>
+      </c>
+      <c r="E10" t="str">
+        <v>SINDU/9829/833.32</v>
+      </c>
+      <c r="F10" t="str">
+        <v>HIDCL/23951/293.61</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>B13</v>
+      </c>
+      <c r="B11" t="str">
+        <v>UNHPL/36014/426.41</v>
+      </c>
+      <c r="C11" t="str">
+        <v>SHPC/18115/609.62</v>
+      </c>
+      <c r="D11" t="str">
+        <v>SAPDBL/8517/1,082.23</v>
+      </c>
+      <c r="E11" t="str">
+        <v>RHPL/24241/352.73</v>
+      </c>
+      <c r="F11" t="str">
+        <v>PRIN/8023/911.61</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>B14</v>
+      </c>
+      <c r="B12" t="str">
+        <v>HBL/346606/238.00</v>
+      </c>
+      <c r="C12" t="str">
+        <v>SANIMA/186696/346.46</v>
+      </c>
+      <c r="D12" t="str">
+        <v>SKBBL/55195/902.11</v>
+      </c>
+      <c r="E12" t="str">
+        <v>CGH/48032/987.10</v>
+      </c>
+      <c r="F12" t="str">
+        <v>GBIME/164913/247.31</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>B16</v>
+      </c>
+      <c r="B13" t="str">
+        <v>MEN/164441/620.40</v>
+      </c>
+      <c r="C13" t="str">
+        <v>CHDC/30786/2,615.51</v>
+      </c>
+      <c r="D13" t="str">
+        <v>SHL/100966/563.48</v>
+      </c>
+      <c r="E13" t="str">
+        <v>RADHI/60298/799.25</v>
+      </c>
+      <c r="F13" t="str">
+        <v>HIDCLP/180157/210.32</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>B17</v>
+      </c>
+      <c r="B14" t="str">
+        <v>SANIMA/274117/343.19</v>
+      </c>
+      <c r="C14" t="str">
+        <v>UPCL/224629/415.44</v>
+      </c>
+      <c r="D14" t="str">
+        <v>HRL/89837/952.94</v>
+      </c>
+      <c r="E14" t="str">
+        <v>KBL/373216/217.53</v>
+      </c>
+      <c r="F14" t="str">
+        <v>EBL/110829/669.76</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>B18</v>
+      </c>
+      <c r="B15" t="str">
+        <v>NGPL/113777/395.09</v>
+      </c>
+      <c r="C15" t="str">
+        <v>AKPL/156388/265.31</v>
+      </c>
+      <c r="D15" t="str">
+        <v>SANIMA/52623/370.85</v>
+      </c>
+      <c r="E15" t="str">
+        <v>LICN/20570/904.79</v>
+      </c>
+      <c r="F15" t="str">
+        <v>BARUN/30194/434.01</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>B19</v>
+      </c>
+      <c r="B16" t="str">
+        <v>JBBL/101843/370.96</v>
+      </c>
+      <c r="C16" t="str">
+        <v>UNHPL/44883/443.35</v>
+      </c>
+      <c r="D16" t="str">
+        <v>SHEL/57036/296.28</v>
+      </c>
+      <c r="E16" t="str">
+        <v>UMHL/24006/571.51</v>
+      </c>
+      <c r="F16" t="str">
+        <v>HLI/29970/411.68</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>B20</v>
+      </c>
+      <c r="B17" t="str">
+        <v>SPIL/33838/815.81</v>
+      </c>
+      <c r="C17" t="str">
+        <v>PCBL/92942/257.74</v>
+      </c>
+      <c r="D17" t="str">
+        <v>RADHI/28419/799.84</v>
+      </c>
+      <c r="E17" t="str">
+        <v>CHCL/25806/545.74</v>
+      </c>
+      <c r="F17" t="str">
+        <v>SHPC/17763/617.47</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>B21</v>
+      </c>
+      <c r="B18" t="str">
+        <v>SAPDBL/12987/1,049.47</v>
+      </c>
+      <c r="C18" t="str">
+        <v>BPCL/10915/872.39</v>
+      </c>
+      <c r="D18" t="str">
+        <v>SPDL/31790/412.92</v>
+      </c>
+      <c r="E18" t="str">
+        <v>SHPC/19319/609.42</v>
+      </c>
+      <c r="F18" t="str">
+        <v>MBJC/30385/325.83</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>B22</v>
+      </c>
+      <c r="B19" t="str">
+        <v>HIDCLP/88277/210.29</v>
+      </c>
+      <c r="C19" t="str">
+        <v>LSL/78050/228.17</v>
+      </c>
+      <c r="D19" t="str">
+        <v>NMB/58437/254.71</v>
+      </c>
+      <c r="E19" t="str">
+        <v>SHEL/50415/294.28</v>
+      </c>
+      <c r="F19" t="str">
+        <v>SHPC/23383/608.88</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>B25</v>
+      </c>
+      <c r="B20" t="str">
+        <v>MNBBL/114591/383.24</v>
+      </c>
+      <c r="C20" t="str">
+        <v>KBL/91188/216.03</v>
+      </c>
+      <c r="D20" t="str">
+        <v>AKPL/62824/264.65</v>
+      </c>
+      <c r="E20" t="str">
+        <v>HIDCLP/70126/210.41</v>
+      </c>
+      <c r="F20" t="str">
+        <v>SAHAS/23032/609.68</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>B26</v>
+      </c>
+      <c r="B21" t="str">
+        <v>NICA/114020/406.00</v>
+      </c>
+      <c r="C21" t="str">
+        <v>RADHI/29286/803.54</v>
+      </c>
+      <c r="D21" t="str">
+        <v>CHCL/46183/538.39</v>
+      </c>
+      <c r="E21" t="str">
+        <v>SAHAS/33228/608.86</v>
+      </c>
+      <c r="F21" t="str">
+        <v>MBL/80706/239.97</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>B28</v>
+      </c>
+      <c r="B22" t="str">
+        <v>SAHAS/173161/598.29</v>
+      </c>
+      <c r="C22" t="str">
+        <v>SHEL/323657/291.20</v>
+      </c>
+      <c r="D22" t="str">
+        <v>GBIME/294952/253.03</v>
+      </c>
+      <c r="E22" t="str">
+        <v>MEN/68048/648.57</v>
+      </c>
+      <c r="F22" t="str">
+        <v>BPCL/56218/850.51</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>B29</v>
+      </c>
+      <c r="B23" t="str">
+        <v>UMHL/93578/564.62</v>
+      </c>
+      <c r="C23" t="str">
+        <v>NRN/19123/2,269.02</v>
+      </c>
+      <c r="D23" t="str">
+        <v>JBBL/51894/371.03</v>
+      </c>
+      <c r="E23" t="str">
+        <v>HRL/19844/966.33</v>
+      </c>
+      <c r="F23" t="str">
+        <v>GRDBL/13326/1,391.93</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>B32</v>
+      </c>
+      <c r="B24" t="str">
+        <v>NRN/76826/2,168.70</v>
+      </c>
+      <c r="C24" t="str">
+        <v>BPCL/87230/888.89</v>
+      </c>
+      <c r="D24" t="str">
+        <v>CHDC/22077/2,671.66</v>
+      </c>
+      <c r="E24" t="str">
+        <v>HIDCLP/266898/209.37</v>
+      </c>
+      <c r="F24" t="str">
+        <v>HIDCL/156315/294.97</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>B33</v>
+      </c>
+      <c r="B25" t="str">
+        <v>SANIMA/297111/353.48</v>
+      </c>
+      <c r="C25" t="str">
+        <v>SBI/236302/425.93</v>
+      </c>
+      <c r="D25" t="str">
+        <v>SADBL/220617/433.57</v>
+      </c>
+      <c r="E25" t="str">
+        <v>EBL/102034/718.07</v>
+      </c>
+      <c r="F25" t="str">
+        <v>LSL/300415/232.99</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>B34</v>
+      </c>
+      <c r="B26" t="str">
+        <v>SHPC/124628/611.09</v>
+      </c>
+      <c r="C26" t="str">
+        <v>SBL/181459/368.09</v>
+      </c>
+      <c r="D26" t="str">
+        <v>MKHL/60214/826.42</v>
+      </c>
+      <c r="E26" t="str">
+        <v>NLIC/39805/792.32</v>
+      </c>
+      <c r="F26" t="str">
+        <v>BARUN/76599/423.32</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>B35</v>
+      </c>
+      <c r="B27" t="str">
+        <v>HBL/187809/242.34</v>
+      </c>
+      <c r="C27" t="str">
+        <v>CHDC/13658/2,660.42</v>
+      </c>
+      <c r="D27" t="str">
+        <v>LBBL/64988/495.52</v>
+      </c>
+      <c r="E27" t="str">
+        <v>HIDCL/97383/296.13</v>
+      </c>
+      <c r="F27" t="str">
+        <v>NGPL/57341/399.65</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>B36</v>
+      </c>
+      <c r="B28" t="str">
+        <v>SAPDBL/26232/1,051.85</v>
+      </c>
+      <c r="C28" t="str">
+        <v>LSL/101092/227.88</v>
+      </c>
+      <c r="D28" t="str">
+        <v>SHINE/37949/438.93</v>
+      </c>
+      <c r="E28" t="str">
+        <v>CBBL/15699/1,017.45</v>
+      </c>
+      <c r="F28" t="str">
+        <v>GBIME/56195/251.12</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>B37</v>
+      </c>
+      <c r="B29" t="str">
+        <v>NICA/24870/406.98</v>
+      </c>
+      <c r="C29" t="str">
+        <v>SHPC/16417/613.63</v>
+      </c>
+      <c r="D29" t="str">
+        <v>RFPL/9332/629.89</v>
+      </c>
+      <c r="E29" t="str">
+        <v>LEC/27026/215.25</v>
+      </c>
+      <c r="F29" t="str">
+        <v>SHL/9471/568.70</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>B38</v>
+      </c>
+      <c r="B30" t="str">
+        <v>RSDC/74625/738.81</v>
+      </c>
+      <c r="C30" t="str">
+        <v>RADHI/42508/806.77</v>
+      </c>
+      <c r="D30" t="str">
+        <v>SAPDBL/32624/1,056.79</v>
+      </c>
+      <c r="E30" t="str">
+        <v>CZBIL/119204/229.12</v>
+      </c>
+      <c r="F30" t="str">
+        <v>BPCL/24485/863.21</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>B39</v>
+      </c>
+      <c r="B31" t="str">
+        <v>UNHPL/227396/446.22</v>
+      </c>
+      <c r="C31" t="str">
+        <v>RADHI/117109/796.56</v>
+      </c>
+      <c r="D31" t="str">
+        <v>NBL/214375/268.88</v>
+      </c>
+      <c r="E31" t="str">
+        <v>HIDCL/139354/304.44</v>
+      </c>
+      <c r="F31" t="str">
+        <v>SADBL/63487/432.05</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>B40</v>
+      </c>
+      <c r="B32" t="str">
+        <v>SMATA/19714/828.05</v>
+      </c>
+      <c r="C32" t="str">
+        <v>BPCL/17480/856.01</v>
+      </c>
+      <c r="D32" t="str">
+        <v>RADHI/17595/796.79</v>
+      </c>
+      <c r="E32" t="str">
+        <v>CHCL/23825/539.72</v>
+      </c>
+      <c r="F32" t="str">
+        <v>NLICL/18016/615.13</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>B41</v>
+      </c>
+      <c r="B33" t="str">
+        <v>GRDBL/65177/1,467.40</v>
+      </c>
+      <c r="C33" t="str">
+        <v>BHDC/136914/535.96</v>
+      </c>
+      <c r="D33" t="str">
+        <v>DORDI/140637/329.71</v>
+      </c>
+      <c r="E33" t="str">
+        <v>SINDU/35803/896.74</v>
+      </c>
+      <c r="F33" t="str">
+        <v>PMHPL/48147/407.95</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>B42</v>
+      </c>
+      <c r="B34" t="str">
+        <v>MERO/154814/844.25</v>
+      </c>
+      <c r="C34" t="str">
+        <v>SHEL/275434/296.33</v>
+      </c>
+      <c r="D34" t="str">
+        <v>NGPL/105974/397.27</v>
+      </c>
+      <c r="E34" t="str">
+        <v>PRIN/45350/916.27</v>
+      </c>
+      <c r="F34" t="str">
+        <v>SONA/73793/461.22</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>B43</v>
+      </c>
+      <c r="B35" t="str">
+        <v>KBL/186778/211.65</v>
+      </c>
+      <c r="C35" t="str">
+        <v>SANIMA/75313/368.13</v>
+      </c>
+      <c r="D35" t="str">
+        <v>BPCL/34671/858.97</v>
+      </c>
+      <c r="E35" t="str">
+        <v>HDL/17432/1,226.81</v>
+      </c>
+      <c r="F35" t="str">
+        <v>PRVU/93151/215.91</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>B44</v>
+      </c>
+      <c r="B36" t="str">
+        <v>NGPL/468615/401.65</v>
+      </c>
+      <c r="C36" t="str">
+        <v>EBL/95238/712.38</v>
+      </c>
+      <c r="D36" t="str">
+        <v>ALICL/94671/504.93</v>
+      </c>
+      <c r="E36" t="str">
+        <v>SHIVM/91899/531.91</v>
+      </c>
+      <c r="F36" t="str">
+        <v>EDBL/68482/606.21</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>B45</v>
+      </c>
+      <c r="B37" t="str">
+        <v>NICA/471773/404.61</v>
+      </c>
+      <c r="C37" t="str">
+        <v>BARUN/134883/429.25</v>
+      </c>
+      <c r="D37" t="str">
+        <v>LBBL/70064/495.15</v>
+      </c>
+      <c r="E37" t="str">
+        <v>RADHI/41078/805.06</v>
+      </c>
+      <c r="F37" t="str">
+        <v>MLBL/68311/412.20</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>B46</v>
+      </c>
+      <c r="B38" t="str">
+        <v>RADHI/14844/795.92</v>
+      </c>
+      <c r="C38" t="str">
+        <v>TAMOR/21430/519.29</v>
+      </c>
+      <c r="D38" t="str">
+        <v>BHL/41335/216.02</v>
+      </c>
+      <c r="E38" t="str">
+        <v>SAPDBL/8013/1,058.62</v>
+      </c>
+      <c r="F38" t="str">
+        <v>SANIMA/19885/359.93</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>B47</v>
+      </c>
+      <c r="B39" t="str">
+        <v>NRN/19922/2,244.40</v>
+      </c>
+      <c r="C39" t="str">
+        <v>KBL/146390/215.78</v>
+      </c>
+      <c r="D39" t="str">
+        <v>RADHI/27598/800.10</v>
+      </c>
+      <c r="E39" t="str">
+        <v>CGH/19277/1,003.16</v>
+      </c>
+      <c r="F39" t="str">
+        <v>SAPDBL/13379/1,045.93</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>B48</v>
+      </c>
+      <c r="B40" t="str">
+        <v>SMATA/77293/905.68</v>
+      </c>
+      <c r="C40" t="str">
+        <v>NBL/215305/295.07</v>
+      </c>
+      <c r="D40" t="str">
+        <v>GBIME/225977/252.89</v>
+      </c>
+      <c r="E40" t="str">
+        <v>SHPC/73978/611.67</v>
+      </c>
+      <c r="F40" t="str">
+        <v>SBL/91649/361.15</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>B49</v>
+      </c>
+      <c r="B41" t="str">
+        <v>MDB/86441/661.04</v>
+      </c>
+      <c r="C41" t="str">
+        <v>SADBL/79724/445.31</v>
+      </c>
+      <c r="D41" t="str">
+        <v>RHPL/70764/361.65</v>
+      </c>
+      <c r="E41" t="str">
+        <v>KSBBL/50436/498.87</v>
+      </c>
+      <c r="F41" t="str">
+        <v>SALICO/34757/715.32</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>B50</v>
+      </c>
+      <c r="B42" t="str">
+        <v>GBBL/144584/449.05</v>
+      </c>
+      <c r="C42" t="str">
+        <v>KSBBL/112385/522.59</v>
+      </c>
+      <c r="D42" t="str">
+        <v>MNBBL/84961/433.72</v>
+      </c>
+      <c r="E42" t="str">
+        <v>SAHAS/53938/622.30</v>
+      </c>
+      <c r="F42" t="str">
+        <v>TAMOR/68156/516.44</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>B51</v>
+      </c>
+      <c r="B43" t="str">
+        <v>CHDC/6987/2,649.23</v>
+      </c>
+      <c r="C43" t="str">
+        <v>SAPDBL/15975/1,048.18</v>
+      </c>
+      <c r="D43" t="str">
+        <v>NGPL/33452/398.14</v>
+      </c>
+      <c r="E43" t="str">
+        <v>BHL/46035/213.35</v>
+      </c>
+      <c r="F43" t="str">
+        <v>CGH/10184/975.85</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>B52</v>
+      </c>
+      <c r="B44" t="str">
+        <v>NABIL/204539/535.35</v>
+      </c>
+      <c r="C44" t="str">
+        <v>NBL/251698/294.11</v>
+      </c>
+      <c r="D44" t="str">
+        <v>SCB/88375/661.98</v>
+      </c>
+      <c r="E44" t="str">
+        <v>PCBL/168021/280.04</v>
+      </c>
+      <c r="F44" t="str">
+        <v>EBL/54570/701.24</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>B53</v>
+      </c>
+      <c r="B45" t="str">
+        <v>SHPC/23681/607.23</v>
+      </c>
+      <c r="C45" t="str">
+        <v>HRL/13037/967.68</v>
+      </c>
+      <c r="D45" t="str">
+        <v>AHPC/40847/288.74</v>
+      </c>
+      <c r="E45" t="str">
+        <v>HIDCLP/52161/213.53</v>
+      </c>
+      <c r="F45" t="str">
+        <v>SAHAS/16526/615.09</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>B54</v>
+      </c>
+      <c r="B46" t="str">
+        <v>STC/12894/5,136.72</v>
+      </c>
+      <c r="C46" t="str">
+        <v>HRL/31064/988.81</v>
+      </c>
+      <c r="D46" t="str">
+        <v>EDBL/27951/662.30</v>
+      </c>
+      <c r="E46" t="str">
+        <v>CBBL/16980/954.49</v>
+      </c>
+      <c r="F46" t="str">
+        <v>SWBBL/17886/833.79</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>B55</v>
+      </c>
+      <c r="B47" t="str">
+        <v>NRIC/995395/1,342.72</v>
+      </c>
+      <c r="C47" t="str">
+        <v>GMLI/45835/2,341.86</v>
+      </c>
+      <c r="D47" t="str">
+        <v>NMIC/59313/1,648.20</v>
+      </c>
+      <c r="E47" t="str">
+        <v>RADHI/50735/808.13</v>
+      </c>
+      <c r="F47" t="str">
+        <v>CHDC/12778/2,658.70</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>B56</v>
+      </c>
+      <c r="B48" t="str">
+        <v>CHDC/39812/2,749.42</v>
+      </c>
+      <c r="C48" t="str">
+        <v>SARBTM/120236/857.89</v>
+      </c>
+      <c r="D48" t="str">
+        <v>BPCL/93144/852.83</v>
+      </c>
+      <c r="E48" t="str">
+        <v>SBL/144150/349.34</v>
+      </c>
+      <c r="F48" t="str">
+        <v>PCBL/157863/278.68</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>B57</v>
+      </c>
+      <c r="B49" t="str">
+        <v>RADHI/52399/803.71</v>
+      </c>
+      <c r="C49" t="str">
+        <v>SAPDBL/33111/1,052.66</v>
+      </c>
+      <c r="D49" t="str">
+        <v>PRIN/35968/917.49</v>
+      </c>
+      <c r="E49" t="str">
+        <v>SAHAS/38896/609.65</v>
+      </c>
+      <c r="F49" t="str">
+        <v>RIDI/87074/262.95</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>B58</v>
+      </c>
+      <c r="B50" t="str">
+        <v>FMDBL/524631/866.32</v>
+      </c>
+      <c r="C50" t="str">
+        <v>RADHI/143672/801.54</v>
+      </c>
+      <c r="D50" t="str">
+        <v>LBBL/189497/514.96</v>
+      </c>
+      <c r="E50" t="str">
+        <v>KSBBL/200042/502.09</v>
+      </c>
+      <c r="F50" t="str">
+        <v>NGPL/226600/399.85</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>B59</v>
+      </c>
+      <c r="B51" t="str">
+        <v>RADHI/69546/800.72</v>
+      </c>
+      <c r="C51" t="str">
+        <v>DORDI/76745/332.20</v>
+      </c>
+      <c r="D51" t="str">
+        <v>NLIC/31147/793.35</v>
+      </c>
+      <c r="E51" t="str">
+        <v>SHPC/34694/611.01</v>
+      </c>
+      <c r="F51" t="str">
+        <v>NRN/9113/2,210.68</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>B60</v>
+      </c>
+      <c r="B52" t="str">
+        <v>GRDBL/37330/1,428.65</v>
+      </c>
+      <c r="C52" t="str">
+        <v>SHIVM/63831/559.07</v>
+      </c>
+      <c r="D52" t="str">
+        <v>CZBIL/93423/228.37</v>
+      </c>
+      <c r="E52" t="str">
+        <v>OMPL/15044/1,403.73</v>
+      </c>
+      <c r="F52" t="str">
+        <v>GHL/70054/268.37</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>B61</v>
+      </c>
+      <c r="B53" t="str">
+        <v>CHDC/11659/2,683.50</v>
+      </c>
+      <c r="C53" t="str">
+        <v>NRN/13347/2,240.26</v>
+      </c>
+      <c r="D53" t="str">
+        <v>HRL/23462/999.65</v>
+      </c>
+      <c r="E53" t="str">
+        <v>NRIC/9717/1,416.89</v>
+      </c>
+      <c r="F53" t="str">
+        <v>SADBL/25325/459.90</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>B62</v>
+      </c>
+      <c r="B54" t="str">
+        <v>UMHL/315438/557.50</v>
+      </c>
+      <c r="C54" t="str">
+        <v>BPCL/109379/870.13</v>
+      </c>
+      <c r="D54" t="str">
+        <v>UNHPL/111444/441.72</v>
+      </c>
+      <c r="E54" t="str">
+        <v>SARBTM/47228/860.39</v>
+      </c>
+      <c r="F54" t="str">
+        <v>ANLB/6728/5,383.19</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>B63</v>
+      </c>
+      <c r="B55" t="str">
+        <v>MERO/44659/875.55</v>
+      </c>
+      <c r="C55" t="str">
+        <v>USLB/14466/1,902.92</v>
+      </c>
+      <c r="D55" t="str">
+        <v>HBL/115837/239.00</v>
+      </c>
+      <c r="E55" t="str">
+        <v>CHDC/7007/2,634.50</v>
+      </c>
+      <c r="F55" t="str">
+        <v>HRL/17818/988.02</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>B64</v>
+      </c>
+      <c r="B56" t="str">
+        <v>BPCL/222296/866.97</v>
+      </c>
+      <c r="C56" t="str">
+        <v>SPIL/100641/800.47</v>
+      </c>
+      <c r="D56" t="str">
+        <v>MSHL/63539/887.78</v>
+      </c>
+      <c r="E56" t="str">
+        <v>BHDC/85887/537.06</v>
+      </c>
+      <c r="F56" t="str">
+        <v>TSHL/33322/848.88</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>B65</v>
+      </c>
+      <c r="B57" t="str">
+        <v>SBI/353639/434.31</v>
+      </c>
+      <c r="C57" t="str">
+        <v>SMHL/66848/1,039.84</v>
+      </c>
+      <c r="D57" t="str">
+        <v>CHCL/108024/540.53</v>
+      </c>
+      <c r="E57" t="str">
+        <v>SPIL/63635/811.23</v>
+      </c>
+      <c r="F57" t="str">
+        <v>HIDCLP/232316/211.95</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>B66</v>
+      </c>
+      <c r="B58" t="str">
+        <v>SARBTM/87854/888.56</v>
+      </c>
+      <c r="C58" t="str">
+        <v>API/214817/294.84</v>
+      </c>
+      <c r="D58" t="str">
+        <v>SAHAS/93164/607.77</v>
+      </c>
+      <c r="E58" t="str">
+        <v>NRN/14695/2,225.74</v>
+      </c>
+      <c r="F58" t="str">
+        <v>NRIC/11940/1,386.57</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>B67</v>
+      </c>
+      <c r="B59" t="str">
+        <v>BPCL/40496/866.15</v>
+      </c>
+      <c r="C59" t="str">
+        <v>UPPER/120583/211.15</v>
+      </c>
+      <c r="D59" t="str">
+        <v>RADHI/27481/803.14</v>
+      </c>
+      <c r="E59" t="str">
+        <v>SKBBL/13301/935.76</v>
+      </c>
+      <c r="F59" t="str">
+        <v>MBL/45516/258.77</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>B68</v>
+      </c>
+      <c r="B60" t="str">
+        <v>SPC/65080/533.54</v>
+      </c>
+      <c r="C60" t="str">
+        <v>OMPL/17111/1,392.02</v>
+      </c>
+      <c r="D60" t="str">
+        <v>NUBL/13970/791.15</v>
+      </c>
+      <c r="E60" t="str">
+        <v>SHL/18400/580.16</v>
+      </c>
+      <c r="F60" t="str">
+        <v>CZBIL/36034/226.61</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>B69</v>
+      </c>
+      <c r="B61" t="str">
+        <v>NGPL/104308/395.52</v>
+      </c>
+      <c r="C61" t="str">
+        <v>SAHAS/62177/622.27</v>
+      </c>
+      <c r="D61" t="str">
+        <v>SHL/50022/580.80</v>
+      </c>
+      <c r="E61" t="str">
+        <v>SBL/74591/361.45</v>
+      </c>
+      <c r="F61" t="str">
+        <v>SPDL/53284/423.41</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>B70</v>
+      </c>
+      <c r="B62" t="str">
+        <v>BEDC/88015/704.19</v>
+      </c>
+      <c r="C62" t="str">
+        <v>SHPC/56408/618.98</v>
+      </c>
+      <c r="D62" t="str">
+        <v>SANIMA/62450/376.75</v>
+      </c>
+      <c r="E62" t="str">
+        <v>CHDC/7393/2,716.54</v>
+      </c>
+      <c r="F62" t="str">
+        <v>HRL/18293/965.17</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>B71</v>
+      </c>
+      <c r="B63" t="str">
+        <v>NRIC/37593/1,335.48</v>
+      </c>
+      <c r="C63" t="str">
+        <v>SPIL/35708/830.49</v>
+      </c>
+      <c r="D63" t="str">
+        <v>SHIVM/49634/556.17</v>
+      </c>
+      <c r="E63" t="str">
+        <v>CORBL/11005/2,355.65</v>
+      </c>
+      <c r="F63" t="str">
+        <v>SALICO/27286/732.05</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>B72</v>
+      </c>
+      <c r="B64" t="str">
+        <v>SAPDBL/28166/1,068.07</v>
+      </c>
+      <c r="C64" t="str">
+        <v>ULHC/51737/494.37</v>
+      </c>
+      <c r="D64" t="str">
+        <v>PMHPL/35010/410.16</v>
+      </c>
+      <c r="E64" t="str">
+        <v>RADHI/8928/806.84</v>
+      </c>
+      <c r="F64" t="str">
+        <v>MNBBL/20443/401.20</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>B73</v>
+      </c>
+      <c r="B65" t="str">
+        <v>SHEL/1000/299.97</v>
+      </c>
+      <c r="C65" t="str">
+        <v>NRM/500/430.00</v>
+      </c>
+      <c r="D65" t="str">
+        <v>BARUN/500/420.50</v>
+      </c>
+      <c r="E65" t="str">
+        <v>BHL/330/206.00</v>
+      </c>
+      <c r="F65" t="str">
+        <v>VLBS/64/787.00</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>B74</v>
+      </c>
+      <c r="B66" t="str">
+        <v>HRL/43480/983.54</v>
+      </c>
+      <c r="C66" t="str">
+        <v>SKBBL/46501/913.12</v>
+      </c>
+      <c r="D66" t="str">
+        <v>AVYAN/30970/1,094.88</v>
+      </c>
+      <c r="E66" t="str">
+        <v>CZBIL/91901/212.46</v>
+      </c>
+      <c r="F66" t="str">
+        <v>SADBL/34861/444.84</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>B75</v>
+      </c>
+      <c r="B67" t="str">
+        <v>NRN/18005/2,274.84</v>
+      </c>
+      <c r="C67" t="str">
+        <v>SAHAS/45881/589.79</v>
+      </c>
+      <c r="D67" t="str">
+        <v>LBBL/35196/506.74</v>
+      </c>
+      <c r="E67" t="str">
+        <v>SHIVM/31865/561.06</v>
+      </c>
+      <c r="F67" t="str">
+        <v>SKBBL/12762/896.38</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>B76</v>
+      </c>
+      <c r="B68" t="str">
+        <v>SAHAS/45843/628.15</v>
+      </c>
+      <c r="C68" t="str">
+        <v>API/42380/300.25</v>
+      </c>
+      <c r="D68" t="str">
+        <v>NRN/4968/2,360.00</v>
+      </c>
+      <c r="E68" t="str">
+        <v>MBJC/17689/318.22</v>
+      </c>
+      <c r="F68" t="str">
+        <v>UPCL/7970/425.82</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>B77</v>
+      </c>
+      <c r="B69" t="str">
+        <v>NRN/48760/2,249.45</v>
+      </c>
+      <c r="C69" t="str">
+        <v>CHDC/22716/2,695.55</v>
+      </c>
+      <c r="D69" t="str">
+        <v>NLIC/46552/819.03</v>
+      </c>
+      <c r="E69" t="str">
+        <v>BPCL/37753/875.09</v>
+      </c>
+      <c r="F69" t="str">
+        <v>SAHAS/48068/624.64</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>B78</v>
+      </c>
+      <c r="B70" t="str">
+        <v>RADHI/16695/803.57</v>
+      </c>
+      <c r="C70" t="str">
+        <v>HDL/4700/1,228.70</v>
+      </c>
+      <c r="D70" t="str">
+        <v>RFPL/9560/612.42</v>
+      </c>
+      <c r="E70" t="str">
+        <v>NICA/10300/403.80</v>
+      </c>
+      <c r="F70" t="str">
+        <v>GVL/8964/473.99</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>B79</v>
+      </c>
+      <c r="B71" t="str">
+        <v>SHEL/3470/290.71</v>
+      </c>
+      <c r="C71" t="str">
+        <v>JBBL/2501/356.75</v>
+      </c>
+      <c r="D71" t="str">
+        <v>NMIC/482/1,756.93</v>
+      </c>
+      <c r="E71" t="str">
+        <v>PRVU/2567/205.34</v>
+      </c>
+      <c r="F71" t="str">
+        <v>NICA/1063/417.97</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>B80</v>
+      </c>
+      <c r="B72" t="str">
+        <v>BPCL/97676/897.64</v>
+      </c>
+      <c r="C72" t="str">
+        <v>RADHI/30166/803.44</v>
+      </c>
+      <c r="D72" t="str">
+        <v>BHDC/36538/544.98</v>
+      </c>
+      <c r="E72" t="str">
+        <v>TSHL/23006/779.91</v>
+      </c>
+      <c r="F72" t="str">
+        <v>BEDC/25063/685.75</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>B81</v>
+      </c>
+      <c r="B73" t="str">
+        <v>RADHI/222121/812.60</v>
+      </c>
+      <c r="C73" t="str">
+        <v>CHCL/133623/542.85</v>
+      </c>
+      <c r="D73" t="str">
+        <v>LSL/291842/238.23</v>
+      </c>
+      <c r="E73" t="str">
+        <v>NGPL/155420/398.09</v>
+      </c>
+      <c r="F73" t="str">
+        <v>HRL/60580/952.27</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>B82</v>
+      </c>
+      <c r="B74" t="str">
+        <v>RSDC/9900/794.96</v>
+      </c>
+      <c r="C74" t="str">
+        <v>MNBBL/17500/433.26</v>
+      </c>
+      <c r="D74" t="str">
+        <v>SADBL/15180/445.31</v>
+      </c>
+      <c r="E74" t="str">
+        <v>HIDCL/20724/303.99</v>
+      </c>
+      <c r="F74" t="str">
+        <v>HRL/5024/974.76</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>B83</v>
+      </c>
+      <c r="B75" t="str">
+        <v>BPCL/21561/888.46</v>
+      </c>
+      <c r="C75" t="str">
+        <v>LICN/19608/894.91</v>
+      </c>
+      <c r="D75" t="str">
+        <v>SADBL/35346/451.99</v>
+      </c>
+      <c r="E75" t="str">
+        <v>KSBBL/23111/495.20</v>
+      </c>
+      <c r="F75" t="str">
+        <v>HRL/10621/988.24</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>B84</v>
+      </c>
+      <c r="B76" t="str">
+        <v>NGPL/284017/402.78</v>
+      </c>
+      <c r="C76" t="str">
+        <v>MKHL/110878/838.08</v>
+      </c>
+      <c r="D76" t="str">
+        <v>SPL/39368/923.36</v>
+      </c>
+      <c r="E76" t="str">
+        <v>NBL/68958/289.25</v>
+      </c>
+      <c r="F76" t="str">
+        <v>CBBL/17605/953.31</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>B85</v>
+      </c>
+      <c r="B77" t="str">
+        <v>LBBL/54044/499.87</v>
+      </c>
+      <c r="C77" t="str">
+        <v>SHPC/34103/614.59</v>
+      </c>
+      <c r="D77" t="str">
+        <v>MNBBL/28239/434.83</v>
+      </c>
+      <c r="E77" t="str">
+        <v>GBBL/27870/445.19</v>
+      </c>
+      <c r="F77" t="str">
+        <v>NLIC/13393/771.86</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>B86</v>
+      </c>
+      <c r="B78" t="str">
+        <v>NRIC/9107/1,397.39</v>
+      </c>
+      <c r="C78" t="str">
+        <v>NRN/2842/2,264.97</v>
+      </c>
+      <c r="D78" t="str">
+        <v>GLH/20673/285.84</v>
+      </c>
+      <c r="E78" t="str">
+        <v>UNHPL/12112/437.93</v>
+      </c>
+      <c r="F78" t="str">
+        <v>GVL/10598/467.10</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>B87</v>
+      </c>
+      <c r="B79" t="str">
+        <v>NRIC/9449/1,423.76</v>
+      </c>
+      <c r="C79" t="str">
+        <v>ULBSL/3176/3,357.84</v>
+      </c>
+      <c r="D79" t="str">
+        <v>ANLB/1850/5,439.08</v>
+      </c>
+      <c r="E79" t="str">
+        <v>BHDC/15881/548.35</v>
+      </c>
+      <c r="F79" t="str">
+        <v>NBL/29986/288.96</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>B88</v>
+      </c>
+      <c r="B80" t="str">
+        <v>PMHPL/177273/410.18</v>
+      </c>
+      <c r="C80" t="str">
+        <v>HIDCLP/166702/208.80</v>
+      </c>
+      <c r="D80" t="str">
+        <v>CHDC/11084/2,688.12</v>
+      </c>
+      <c r="E80" t="str">
+        <v>GBBL/61075/442.97</v>
+      </c>
+      <c r="F80" t="str">
+        <v>RADHI/22348/794.03</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>B89</v>
+      </c>
+      <c r="B81" t="str">
+        <v>SANIMA/37251/371.52</v>
+      </c>
+      <c r="C81" t="str">
+        <v>CGH/13437/1,008.45</v>
+      </c>
+      <c r="D81" t="str">
+        <v>NRN/5058/2,211.44</v>
+      </c>
+      <c r="E81" t="str">
+        <v>MERO/14079/834.25</v>
+      </c>
+      <c r="F81" t="str">
+        <v>SICL/9833/786.62</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>B90</v>
+      </c>
+      <c r="B82" t="str">
+        <v>NBL/77387/298.72</v>
+      </c>
+      <c r="C82" t="str">
+        <v>HHL/16472/380.18</v>
+      </c>
+      <c r="D82" t="str">
+        <v>HRL/4448/952.67</v>
+      </c>
+      <c r="E82" t="str">
+        <v>API/10058/292.72</v>
+      </c>
+      <c r="F82" t="str">
+        <v>SJLIC/3685/458.95</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>B91</v>
+      </c>
+      <c r="B83" t="str">
+        <v>DORDI/32581/337.52</v>
+      </c>
+      <c r="C83" t="str">
+        <v>UMHL/12206/563.19</v>
+      </c>
+      <c r="D83" t="str">
+        <v>SHEL/21634/298.87</v>
+      </c>
+      <c r="E83" t="str">
+        <v>SFCL/8964/521.29</v>
+      </c>
+      <c r="F83" t="str">
+        <v>RFPL/7403/618.87</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>B92</v>
+      </c>
+      <c r="B84" t="str">
+        <v>SHPC/90392/629.58</v>
+      </c>
+      <c r="C84" t="str">
+        <v>SBL/100872/386.52</v>
+      </c>
+      <c r="D84" t="str">
+        <v>USLB/9403/2,014.41</v>
+      </c>
+      <c r="E84" t="str">
+        <v>NABIL/33218/549.08</v>
+      </c>
+      <c r="F84" t="str">
+        <v>EBL/12455/718.00</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>B93</v>
+      </c>
+      <c r="B85" t="str">
+        <v>NFS/10256/742.74</v>
+      </c>
+      <c r="C85" t="str">
+        <v>HIDCL/24049/293.25</v>
+      </c>
+      <c r="D85" t="str">
+        <v>NRM/8984/477.10</v>
+      </c>
+      <c r="E85" t="str">
+        <v>MEN/4800/646.11</v>
+      </c>
+      <c r="F85" t="str">
+        <v>SPDL/6900/426.56</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>B94</v>
+      </c>
+      <c r="B86" t="str">
+        <v>SBL/253195/358.44</v>
+      </c>
+      <c r="C86" t="str">
+        <v>MNBBL/114133/435.78</v>
+      </c>
+      <c r="D86" t="str">
+        <v>BPCL/53123/880.39</v>
+      </c>
+      <c r="E86" t="str">
+        <v>KSBBL/44434/526.42</v>
+      </c>
+      <c r="F86" t="str">
+        <v>SANIMA/56411/360.86</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>B95</v>
+      </c>
+      <c r="B87" t="str">
+        <v>HRL/10288/969.80</v>
+      </c>
+      <c r="C87" t="str">
+        <v>RADHI/10934/803.18</v>
+      </c>
+      <c r="D87" t="str">
+        <v>LBBL/15887/493.70</v>
+      </c>
+      <c r="E87" t="str">
+        <v>DORDI/22960/326.58</v>
+      </c>
+      <c r="F87" t="str">
+        <v>NLG/8546/853.67</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>B96</v>
+      </c>
+      <c r="B88" t="str">
+        <v>NRIC/79700/1,390.00</v>
+      </c>
+      <c r="C88" t="str">
+        <v>HRL/40206/988.90</v>
+      </c>
+      <c r="D88" t="str">
+        <v>USLB/16850/1,849.80</v>
+      </c>
+      <c r="E88" t="str">
+        <v>FMDBL/16805/882.74</v>
+      </c>
+      <c r="F88" t="str">
+        <v>EBL/19971/724.94</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>B97</v>
+      </c>
+      <c r="B89" t="str">
+        <v>BPCL/13321/865.07</v>
+      </c>
+      <c r="C89" t="str">
+        <v>SAPDBL/7084/1,058.70</v>
+      </c>
+      <c r="D89" t="str">
+        <v>NRIC/4289/1,356.36</v>
+      </c>
+      <c r="E89" t="str">
+        <v>UPCL/14330/416.16</v>
+      </c>
+      <c r="F89" t="str">
+        <v>NIFRA/11145/293.48</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>B98</v>
+      </c>
+      <c r="B90" t="str">
+        <v>CHCL/31393/544.96</v>
+      </c>
+      <c r="C90" t="str">
+        <v>SAHAS/25681/641.89</v>
+      </c>
+      <c r="D90" t="str">
+        <v>NRIC/9113/1,418.45</v>
+      </c>
+      <c r="E90" t="str">
+        <v>RSDC/17665/784.02</v>
+      </c>
+      <c r="F90" t="str">
+        <v>MKJC/20672/545.36</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>B99</v>
+      </c>
+      <c r="B91" t="str">
+        <v>LBBL/57725/489.00</v>
+      </c>
+      <c r="C91" t="str">
+        <v>BARUN/30921/427.43</v>
+      </c>
+      <c r="D91" t="str">
+        <v>BPCL/11487/855.06</v>
+      </c>
+      <c r="E91" t="str">
+        <v>SAHAS/11943/624.74</v>
+      </c>
+      <c r="F91" t="str">
+        <v>AHPC/23085/297.41</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>B100</v>
+      </c>
+      <c r="B92" t="str">
+        <v>SHPC/88017/593.06</v>
+      </c>
+      <c r="C92" t="str">
+        <v>API/122967/292.55</v>
+      </c>
+      <c r="D92" t="str">
+        <v>NGPL/82498/391.79</v>
+      </c>
+      <c r="E92" t="str">
+        <v>GBBL/62172/421.41</v>
+      </c>
+      <c r="F92" t="str">
+        <v>HURJA/55020/252.48</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>B101</v>
+      </c>
+      <c r="B93" t="str">
+        <v>RADHI/27201/795.12</v>
+      </c>
+      <c r="C93" t="str">
+        <v>SHPC/26449/602.53</v>
+      </c>
+      <c r="D93" t="str">
+        <v>CHDC/4728/2,692.17</v>
+      </c>
+      <c r="E93" t="str">
+        <v>NRN/5350/2,231.34</v>
+      </c>
+      <c r="F93" t="str">
+        <v>NICA/19597/407.09</v>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F93"/>
   </ignoredErrors>
 </worksheet>
 </file>
